--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45953.45833333334</v>
+        <v>45953.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45953.52083333334</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45953.49652777778</v>
+        <v>45953.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.49652777778</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45953.52083333334</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45953.625</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,126 +2950,255 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45953.625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>England EFL League One</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Exeter City</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Plymouth Argyle</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
+      <c r="L21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45953.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45953.45833333334</v>
+        <v>45953.4375</v>
       </c>
     </row>
     <row r="7">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
         <v>3.55</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45953.52083333334</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1839,34 +1839,34 @@
         <v>5.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y11" t="n">
         <v>1.65</v>
@@ -1875,16 +1875,16 @@
         <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45953.41666666666</v>
+        <v>45953.375</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1317,58 +1317,58 @@
         <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2871,52 +2871,52 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,135 +3070,6 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45953.625</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45953</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>England EFL League One</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Exeter City</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Plymouth Argyle</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
         <v>45953.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1317,28 +1317,28 @@
         <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
@@ -1347,28 +1347,28 @@
         <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>3.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1866,7 +1866,7 @@
         <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
         <v>1.65</v>
@@ -1875,7 +1875,7 @@
         <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AB11" t="n">
         <v>1.41</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AH11" t="n">
         <v>2.42</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2871,52 +2871,52 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>5.35</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,34 +3000,34 @@
         <v>2.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
         <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="Y20" t="n">
         <v>1.85</v>
@@ -3036,16 +3036,16 @@
         <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1317,7 +1317,7 @@
         <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
         <v>2.5</v>
@@ -1326,40 +1326,40 @@
         <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
         <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
         <v>1.31</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="AB7" t="n">
         <v>1.28</v>
@@ -1368,7 +1368,7 @@
         <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
         <v>1.44</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
         <v>1.5</v>
@@ -1866,7 +1866,7 @@
         <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Y11" t="n">
         <v>1.65</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
         <v>2.42</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2874,7 +2874,7 @@
         <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
         <v>1.65</v>
@@ -2883,10 +2883,10 @@
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>1.7</v>
@@ -2895,28 +2895,28 @@
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
         <v>1.07</v>
@@ -3003,19 +3003,19 @@
         <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
         <v>1.5</v>
@@ -3024,10 +3024,10 @@
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="Y20" t="n">
         <v>1.85</v>
@@ -3042,10 +3042,10 @@
         <v>1.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="P11" t="n">
         <v>2.38</v>
@@ -1854,7 +1854,7 @@
         <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
         <v>1.5</v>
@@ -1869,10 +1869,10 @@
         <v>4.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
         <v>2.52</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.47</v>
+        <v>2.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X20" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
         <v>3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1314,58 +1314,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.31</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD7" t="n">
         <v>1.95</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2871,52 +2871,52 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>8.07</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.46</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T20" t="n">
         <v>2.67</v>
@@ -3021,31 +3021,31 @@
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.74</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.82</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="T11" t="n">
         <v>2.35</v>
@@ -1866,13 +1866,13 @@
         <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
         <v>2.52</v>
@@ -1884,7 +1884,7 @@
         <v>1.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2871,52 +2871,52 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>8.07</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
         <v>2.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
         <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -3000,28 +3000,28 @@
         <v>2.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
         <v>2.94</v>
       </c>
       <c r="T20" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
         <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
         <v>1.2</v>
@@ -3036,16 +3036,16 @@
         <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
         <v>1.41</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>5.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.42</v>
+        <v>2.52</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>2.41</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45953.5</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45953.52083333334</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
         <v>2.59</v>
@@ -1326,7 +1326,7 @@
         <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
         <v>3.22</v>
@@ -1335,10 +1335,10 @@
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
         <v>1.36</v>
@@ -1365,10 +1365,10 @@
         <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="R8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.4</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.32</v>
       </c>
-      <c r="X8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.95</v>
@@ -1587,7 +1587,7 @@
         <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.55</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
         <v>1.28</v>
@@ -1605,16 +1605,16 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
         <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AA9" t="n">
         <v>2.52</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
         <v>2.41</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
         <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
         <v>1.03</v>
@@ -2898,25 +2898,25 @@
         <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>5.5</v>
+        <v>4.79</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.77</v>
+        <v>2.48</v>
       </c>
       <c r="AA19" t="n">
         <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH19" t="n">
         <v>1.03</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="M20" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
         <v>3.25</v>
@@ -3012,7 +3012,7 @@
         <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
         <v>2.6</v>
@@ -3027,19 +3027,19 @@
         <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>3.54</v>
+        <v>3.93</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AC20" t="n">
         <v>1.62</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
         <v>2.59</v>
@@ -1326,7 +1326,7 @@
         <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
         <v>3.22</v>
@@ -1335,19 +1335,19 @@
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>3.52</v>
@@ -1365,7 +1365,7 @@
         <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
         <v>2.1</v>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45953.49652777778</v>
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
         <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.04</v>
+        <v>3.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
         <v>2.7</v>
@@ -1470,31 +1470,31 @@
         <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="Y8" t="n">
         <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="n">
         <v>3.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
         <v>1.84</v>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.59</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="P9" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O19" t="n">
         <v>7</v>
@@ -2877,13 +2877,13 @@
         <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
         <v>2.27</v>
@@ -2892,31 +2892,31 @@
         <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
         <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
         <v>2.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.11</v>
+        <v>3.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
         <v>3.25</v>
@@ -3012,7 +3012,7 @@
         <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="T20" t="n">
         <v>2.6</v>
@@ -3030,13 +3030,13 @@
         <v>3.93</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AB20" t="n">
         <v>1.34</v>
@@ -3061,7 +3061,7 @@
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,34 +1065,34 @@
         <v>1.33</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y5" t="n">
         <v>1.55</v>
@@ -1101,16 +1101,16 @@
         <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1194,34 +1194,34 @@
         <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y6" t="n">
         <v>1.72</v>
@@ -1230,16 +1230,16 @@
         <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2.5</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.59</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.09</v>
+        <v>3.36</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.46</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.66</v>
+        <v>3.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45953.52083333334</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45953.625</v>
+        <v>45953.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,126 +2950,255 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45953.625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>England EFL League One</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Exeter City</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Plymouth Argyle</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2.47</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>3.21</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>2.47</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>3.25</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1.35</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>2.94</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2.6</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>1.44</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W21" t="n">
         <v>1.2</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X21" t="n">
         <v>3.93</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y21" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z21" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA21" t="n">
         <v>2.8</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AB21" t="n">
         <v>1.34</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC21" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AD21" t="n">
         <v>2.17</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45953.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -807,28 +807,28 @@
         <v>2.02</v>
       </c>
       <c r="O3" t="n">
-        <v>4.33</v>
+        <v>4.98</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
         <v>1.52</v>
@@ -837,22 +837,22 @@
         <v>2.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45953.375</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="M4" t="n">
         <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1065,22 +1065,22 @@
         <v>1.33</v>
       </c>
       <c r="O5" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
@@ -1089,10 +1089,10 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="Y5" t="n">
         <v>1.55</v>
@@ -1101,13 +1101,13 @@
         <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AD5" t="n">
         <v>1.61</v>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1194,34 +1194,34 @@
         <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
         <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="Y6" t="n">
         <v>1.72</v>
@@ -1230,16 +1230,16 @@
         <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45953.4375</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
         <v>2.59</v>
@@ -1335,13 +1335,13 @@
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -1353,7 +1353,7 @@
         <v>3.52</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Z7" t="n">
         <v>1.88</v>
@@ -1365,10 +1365,10 @@
         <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>5.15</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.5</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T9" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.82</v>
+        <v>4.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45953.5</v>
@@ -1710,34 +1710,34 @@
         <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.22</v>
+        <v>5.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="T10" t="n">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1.76</v>
@@ -1746,16 +1746,16 @@
         <v>1.94</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.66</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45953.52083333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
         <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>6.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -3027,25 +3027,25 @@
         <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>4.72</v>
+        <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z20" t="n">
         <v>2.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>3.28</v>
+        <v>1.07</v>
       </c>
       <c r="AH20" t="n">
         <v>1.07</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45953.625</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45953.29166666666</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="N3" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>4.98</v>
+        <v>6.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="R3" t="n">
         <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="T3" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI3" t="n">
         <v>2.6</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="Z4" t="n">
         <v>1.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
         <v>2.05</v>
@@ -1335,40 +1335,40 @@
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.8</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.74</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="Y7" t="n">
         <v>1.92</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M9" t="n">
         <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>2.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.74</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
         <v>1.5</v>
@@ -1611,7 +1611,7 @@
         <v>2.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Z9" t="n">
         <v>1.5</v>
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.17</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q10" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.24</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.06</v>
       </c>
-      <c r="AI10" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45953.52083333334</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45953.54166666666</v>
+        <v>45953.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3156,7 +3156,7 @@
         <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="Y21" t="n">
         <v>1.85</v>
@@ -3165,10 +3165,10 @@
         <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
         <v>1.62</v>
@@ -3190,13 +3190,13 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45953.66666666666</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="O3" t="n">
         <v>6.14</v>
@@ -831,16 +831,16 @@
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>5.2</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="M4" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>3.25</v>
@@ -960,13 +960,13 @@
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="Z4" t="n">
         <v>1.44</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O5" t="n">
         <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
         <v>2.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" t="n">
         <v>3.4</v>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
@@ -1224,10 +1224,10 @@
         <v>3.34</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA6" t="n">
         <v>3.05</v>
@@ -1236,10 +1236,10 @@
         <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI6" t="n">
         <v>2.01</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45953.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45953.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45953.5</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45953.5</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45953.5</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.47</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.38</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" t="n">
         <v>1.53</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -672,7 +672,7 @@
         <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="N2" t="n">
         <v>10</v>
@@ -807,19 +807,19 @@
         <v>2.02</v>
       </c>
       <c r="O3" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
         <v>3.6</v>
@@ -843,16 +843,16 @@
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AB3" t="n">
         <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI3" t="n">
         <v>2.6</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,62 +927,62 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.91</v>
+        <v>7.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>8.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.82</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>3.52</v>
+        <v>2.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.5</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>2.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.3</v>
+        <v>1.91</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.38</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2.59</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>2.19</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.08</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI6" t="n">
         <v>2.01</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
         <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
         <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45953.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45953.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45953.5</v>
@@ -1959,19 +1959,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
         <v>2.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="Q12" t="n">
         <v>4.75</v>
@@ -1986,34 +1986,34 @@
         <v>2.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X12" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA12" t="n">
         <v>3.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
         <v>2.05</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2346,31 +2346,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>4.02</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.32</v>
+        <v>6.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
         <v>1.42</v>
@@ -2382,25 +2382,25 @@
         <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AA15" t="n">
         <v>2.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
         <v>1.44</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O20" t="n">
-        <v>6.38</v>
-      </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AI20" t="n">
         <v>3.5</v>
@@ -3129,34 +3129,34 @@
         <v>2.47</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
         <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
         <v>1.85</v>
@@ -3165,16 +3165,16 @@
         <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
         <v>2.1</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -652,30 +652,30 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="M2" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>3.96</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -708,10 +708,10 @@
         <v>2.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -727,12 +727,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '51']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>5.37</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N3" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="O3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
         <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" t="n">
         <v>2.6</v>
@@ -1056,37 +1056,37 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.91</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
         <v>1.5</v>
@@ -1101,16 +1101,16 @@
         <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
         <v>2.04</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45953.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45953.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45953.5</v>
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.59</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>4.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
         <v>2.11</v>
@@ -1980,40 +1980,40 @@
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>2.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
         <v>3.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="n">
         <v>3.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AI12" t="n">
         <v>1.53</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '73']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -923,65 +923,65 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.5</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>2.85</v>
       </c>
       <c r="O4" t="n">
-        <v>8.5</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>4.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.4</v>
+        <v>2.19</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1020,29 +1020,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>8.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81</v>
+        <v>4.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.59</v>
+        <v>1.83</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
         <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,20 +1119,20 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.19</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1168,94 +1168,94 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="R6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['8', '14']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI6" t="n">
         <v>2.01</v>
@@ -1297,94 +1297,94 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.38</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>2.82</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.29</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '39']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45953.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45953.5</v>
@@ -1942,94 +1942,94 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.45</v>
+        <v>5.91</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="P12" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>6.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="W12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.28</v>
       </c>
-      <c r="X12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '40', '54', '73']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" t="n">
         <v>1.53</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,29 +2310,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2342,87 +2342,87 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65', '79']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12.26</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>9.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AH20" t="n">
         <v>1.02</v>
@@ -3138,16 +3138,16 @@
         <v>2.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
         <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
         <v>1.05</v>
@@ -3156,7 +3156,7 @@
         <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="Y21" t="n">
         <v>1.85</v>
@@ -3165,10 +3165,10 @@
         <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC21" t="n">
         <v>1.65</v>

--- a/jogos_2025-10-23.xlsx
+++ b/jogos_2025-10-23.xlsx
@@ -891,29 +891,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>8.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>4.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.59</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
         <v>2.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.19</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1020,29 +1020,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8.1</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>4.25</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.83</v>
+        <v>2.59</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AC5" t="n">
         <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,20 +1119,20 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>2.19</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45953.41666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45953.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1893,20 +1893,20 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45953.5</v>
@@ -2052,29 +2052,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2084,87 +2084,87 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65', '79']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,29 +2310,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2342,87 +2342,87 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['65', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45953.54166666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2977,17 +2977,17 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG20" t="n">
@@ -3103,82 +3103,82 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="N21" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V21" t="n">
         <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '58']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
